--- a/notebook_modified/Experiment/_summary_reports/_overview.xlsx
+++ b/notebook_modified/Experiment/_summary_reports/_overview.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_Study\Paper\paper_resources\01_src\afw-cil\notebook_modified\Experiment\_summary_reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E39900-E302-4CE3-979A-EF30A60879F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1161A865-D928-4C81-9666-6A5AEED4BA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -445,19 +445,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -500,11 +501,14 @@
         <v>76</v>
       </c>
       <c r="G2" s="1">
-        <f>E2/F2</f>
+        <f t="shared" ref="G2:G11" si="0">E2/F2</f>
         <v>1.8157894736842106</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -524,11 +528,11 @@
         <v>239</v>
       </c>
       <c r="G3" s="1">
-        <f>E3/F3</f>
+        <f t="shared" si="0"/>
         <v>1.8577405857740585</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -548,11 +552,11 @@
         <v>268</v>
       </c>
       <c r="G4" s="1">
-        <f>E4/F4</f>
+        <f t="shared" si="0"/>
         <v>1.8656716417910448</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -572,11 +576,14 @@
         <v>1447</v>
       </c>
       <c r="G5" s="1">
-        <f>E5/F5</f>
+        <f t="shared" si="0"/>
         <v>1.8866620594333103</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -596,11 +603,11 @@
         <v>81</v>
       </c>
       <c r="G6" s="1">
-        <f>E6/F6</f>
+        <f t="shared" si="0"/>
         <v>2.7777777777777777</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -620,11 +627,14 @@
         <v>217</v>
       </c>
       <c r="G7" s="1">
-        <f>E7/F7</f>
+        <f t="shared" si="0"/>
         <v>2.8986175115207375</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -644,11 +654,11 @@
         <v>212</v>
       </c>
       <c r="G8" s="1">
-        <f>E8/F8</f>
+        <f t="shared" si="0"/>
         <v>2.9905660377358489</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -668,11 +678,14 @@
         <v>178</v>
       </c>
       <c r="G9" s="1">
-        <f>E9/F9</f>
+        <f t="shared" si="0"/>
         <v>3.202247191011236</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -692,11 +705,11 @@
         <v>244</v>
       </c>
       <c r="G10" s="1">
-        <f>E10/F10</f>
+        <f t="shared" si="0"/>
         <v>5.081967213114754</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -716,8 +729,11 @@
         <v>220</v>
       </c>
       <c r="G11" s="1">
-        <f>E11/F11</f>
+        <f t="shared" si="0"/>
         <v>29.995454545454546</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
